--- a/artfynd/A 23866-2022 artfynd.xlsx
+++ b/artfynd/A 23866-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 23866-2022 artfynd.xlsx
+++ b/artfynd/A 23866-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>79749988</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522320.1366716251</v>
+        <v>522320</v>
       </c>
       <c r="R2" t="n">
-        <v>6853222.88437075</v>
+        <v>6853223</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2018-10-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-10-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104157786</v>
+        <v>104157781</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,17 +805,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Romberg, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522371.6370037227</v>
+        <v>522419</v>
       </c>
       <c r="R3" t="n">
-        <v>6853238.820154014</v>
+        <v>6853187</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +849,9 @@
           <t>2022-08-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -909,15 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104158339</v>
+        <v>104157782</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -942,17 +911,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Romberg, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522423.913496523</v>
+        <v>522382</v>
       </c>
       <c r="R4" t="n">
-        <v>6853208.434880465</v>
+        <v>6853220</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,22 +952,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-24</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1026,15 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104158340</v>
+        <v>104157783</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522348.2870800543</v>
+        <v>522356</v>
       </c>
       <c r="R5" t="n">
-        <v>6853189.504333026</v>
+        <v>6853246</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,22 +1054,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-24</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1143,15 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104157781</v>
+        <v>104157784</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,21 +1119,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Romberg, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522419.3154426491</v>
+        <v>522341</v>
       </c>
       <c r="R6" t="n">
-        <v>6853187.604775934</v>
+        <v>6853246</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,19 +1159,9 @@
           <t>2022-08-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1264,15 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104157787</v>
+        <v>104157786</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,21 +1221,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Romberg, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>522375.1731838345</v>
+        <v>522371</v>
       </c>
       <c r="R7" t="n">
-        <v>6853204.807109822</v>
+        <v>6853239</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,19 +1261,9 @@
           <t>2022-08-24</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1385,15 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104157782</v>
+        <v>104157787</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,10 +1334,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>522381.7021986954</v>
+        <v>522375</v>
       </c>
       <c r="R8" t="n">
-        <v>6853219.976973876</v>
+        <v>6853205</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,19 +1367,9 @@
           <t>2022-08-24</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1506,15 +1401,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104157783</v>
+        <v>104158339</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1546,10 +1436,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>522355.4947074772</v>
+        <v>522424</v>
       </c>
       <c r="R9" t="n">
-        <v>6853245.805595941</v>
+        <v>6853209</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1576,22 +1466,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1623,15 +1503,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104157784</v>
+        <v>104158340</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,10 +1538,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>522340.3393726515</v>
+        <v>522348</v>
       </c>
       <c r="R10" t="n">
-        <v>6853246.652171768</v>
+        <v>6853190</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1693,22 +1568,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">

--- a/artfynd/A 23866-2022 artfynd.xlsx
+++ b/artfynd/A 23866-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79749988</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104157781</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104157782</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104157783</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1190,6 +1215,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104157784</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1292,6 +1322,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104157786</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1398,6 +1433,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104157787</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1500,6 +1540,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104158339</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1602,8 +1647,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104158340</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>